--- a/data/trans_orig/IP31KM01_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM01_2023-Estudios-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>51201</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>46514</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>53088</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>95,32%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>86,59%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>98,83%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>49926</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>45592</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>52347</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>92,97%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>84,9%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>97,48%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>55673</t>
+          <t>41975</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>50348</t>
+          <t>37632</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>57567</t>
+          <t>44169</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>81,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>105598</t>
+          <t>93176</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>99999</t>
+          <t>87380</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>108998</t>
+          <t>96564</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>96,93%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2514</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>7201</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>4,68%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1,17%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>13,41%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>3773</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1352</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>8107</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>7,03%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>2,52%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>15,1%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2672</t>
+          <t>3930</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>778</t>
+          <t>1736</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7997</t>
+          <t>8273</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>6445</t>
+          <t>6444</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>3056</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12044</t>
+          <t>12240</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>12,29%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>53715</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>53715</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>53715</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>58345</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>58345</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>58345</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>112043</t>
+          <t>99620</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>112043</t>
+          <t>99620</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>112043</t>
+          <t>99620</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>565</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>414049</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>399234</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>426079</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>88,77%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>85,59%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>91,35%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>563</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>410195</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>398700</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>420878</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>90,78%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>88,24%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>93,15%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>565</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>445784</t>
+          <t>382845</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>425350</t>
+          <t>372236</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>459620</t>
+          <t>392822</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>84,19%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>855979</t>
+          <t>796895</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>834244</t>
+          <t>779004</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>872997</t>
+          <t>812228</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,43%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>87,17%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,15%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>52374</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>40344</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>67189</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>11,23%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>8,65%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>14,41%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>41637</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>30954</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>53132</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>9,22%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>6,85%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>11,76%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>59466</t>
+          <t>41821</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>45630</t>
+          <t>31844</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>79900</t>
+          <t>52430</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>101103</t>
+          <t>94195</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>84085</t>
+          <t>78862</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>122838</t>
+          <t>112086</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,58%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>466423</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>466423</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>466423</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>625</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>451832</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>451832</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>451832</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>630</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>505250</t>
+          <t>424666</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>505250</t>
+          <t>424666</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>505250</t>
+          <t>424666</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>957082</t>
+          <t>891090</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>957082</t>
+          <t>891090</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>957082</t>
+          <t>891090</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>152315</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>145126</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>157992</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>91,38%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>87,07%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>94,78%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>206</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>134311</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>127608</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>139042</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>91,88%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>87,29%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>95,11%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>165869</t>
+          <t>135455</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>157601</t>
+          <t>129171</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>172179</t>
+          <t>140005</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>87,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,27 +1481,27 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>300179</t>
+          <t>287770</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>289990</t>
+          <t>278243</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>308067</t>
+          <t>295367</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>88,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>14371</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>8694</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>21560</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>8,62%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>5,22%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>12,93%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>11875</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>7144</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>18578</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>8,12%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>4,89%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>12,71%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>15270</t>
+          <t>11685</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8960</t>
+          <t>7135</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23538</t>
+          <t>17969</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,22 +1594,22 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>27145</t>
+          <t>26055</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>19257</t>
+          <t>18458</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>37334</t>
+          <t>35582</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,34%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>222</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>146186</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>146186</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>146186</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>181139</t>
+          <t>147140</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>181139</t>
+          <t>147140</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>181139</t>
+          <t>147140</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>327324</t>
+          <t>313825</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>327324</t>
+          <t>313825</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>327324</t>
+          <t>313825</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>853</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>617565</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>601064</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>631556</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>89,92%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>87,51%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>91,95%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>830</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>594432</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>579685</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>605742</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>91,21%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>88,95%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>92,95%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>853</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>667324</t>
+          <t>560275</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>646433</t>
+          <t>546112</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>682126</t>
+          <t>572036</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>88,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1261757</t>
+          <t>1177840</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1235964</t>
+          <t>1158313</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1280137</t>
+          <t>1196305</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>91,7%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>69259</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>55268</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>85760</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>10,08%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>8,05%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>12,49%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>84</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>57285</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>45975</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>72032</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>8,79%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>7,05%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>11,05%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>77409</t>
+          <t>57436</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>62607</t>
+          <t>45675</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>98300</t>
+          <t>71599</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>134693</t>
+          <t>126695</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>116313</t>
+          <t>108230</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>160486</t>
+          <t>146222</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,21%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>914</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>651717</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>651717</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>651717</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>617711</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>617711</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>617711</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1396450</t>
+          <t>1304535</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1396450</t>
+          <t>1304535</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1396450</t>
+          <t>1304535</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
